--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251116_201423.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
